--- a/branches/develop/StructureDefinition-mii-pr-person-patient-pseudonymisiert.xlsx
+++ b/branches/develop/StructureDefinition-mii-pr-person-patient-pseudonymisiert.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.0.1</t>
+    <t>2027.0.0-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/branches/develop/StructureDefinition-mii-pr-person-patient-pseudonymisiert.xlsx
+++ b/branches/develop/StructureDefinition-mii-pr-person-patient-pseudonymisiert.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$130</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$138</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4596" uniqueCount="724">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4882" uniqueCount="753">
   <si>
     <t>Property</t>
   </si>
@@ -990,21 +990,17 @@
     <t>Patient.identifier:MaskierterVersichertenIdentifer.extension</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t>Patient.identifier:MaskierterVersichertenIdentifer.use</t>
   </si>
   <si>
     <t>Patient.identifier:MaskierterVersichertenIdentifer.type</t>
   </si>
   <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="http://fhir.de/CodeSystem/identifier-type-de-basis"/&gt;
-    &lt;code value="KVZ10"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
-  </si>
-  <si>
-    <t>http://fhir.de/ValueSet/identifier-type-de-basis</t>
+    <t>http://fhir.de/ValueSet/identifier-type-kvid-de-basis</t>
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
@@ -1064,10 +1060,6 @@
     <t>Provides a reason why the expected value or elements in the element that is extended are missing.</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t>Patient.identifier:MaskierterVersichertenIdentifer.value.extension:data-absent-reason.id</t>
   </si>
   <si>
@@ -1141,6 +1133,14 @@
   </si>
   <si>
     <t>Patient.identifier:MaskierterVersichertenIdentifer.period</t>
+  </si>
+  <si>
+    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
+Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
   </si>
   <si>
     <t>Patient.identifier:MaskierterVersichertenIdentifer.assigner</t>
@@ -1148,6 +1148,10 @@
   <si>
     <t xml:space="preserve">Reference(Organization)
 </t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.exists() implies (reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids')) or (reference='#' and %rootResource!=%resource))}</t>
   </si>
   <si>
     <t>Patient.identifier:MaskierterVersichertenIdentifer.assigner.id</t>
@@ -1266,6 +1270,9 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
+    <t>http://fhir.de/ValueSet/identifier-type-de-basis</t>
+  </si>
+  <si>
     <t>Patient.identifier:MaskierterVersichertenIdentifer.assigner.identifier.system</t>
   </si>
   <si>
@@ -1661,7 +1668,10 @@
   </si>
   <si>
     <t>Diese Komponente kann Straßennamen, Hausnummer, Appartmentnummer, Postfach, c/o sowie weitere Zustellungshinweise enthalten. Die Informationen können in mehrere line-Komponenten aufgeteilt werden.
-Bei Verwendung der Extensions, um Straße, Hausnnummer und Postleitzahl strukturiert zu übermitteln, müssen diese Informationen stets vollständig auch in der line-Komponente, die sie erweitern, enthalten sein, um es Systemen, die diese Extensions nicht verwenden zu ermöglichen, auf diese Informationen zugreifen zu können.</t>
+Bei Verwendung der Extensions, um Straße, Hausnnummer und Postfach strukturiert zu übermitteln, müssen diese Informationen stets vollständig auch in der line-Komponente, die sie erweitern, enthalten sein, um es Systemen, die diese Extensions nicht verwenden zu ermöglichen, auf diese Informationen zugreifen zu können.</t>
+  </si>
+  <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
     <t>137 Nowhere Street</t>
@@ -1897,20 +1907,101 @@
     <t>Staat</t>
   </si>
   <si>
-    <t>Staat (vorzugsweise als 2-Stelliger ISO-Ländercode).
-Es obliegt abgeleiteten Profilen, hier die Verwendung der ISO-Ländercodes verbindlich vorzuschreiben</t>
+    <t>Staatsangabe (ohne festgeschriebenen Wertevorrat)</t>
   </si>
   <si>
     <t>ISO 3166 3 letter codes can be used in place of a human readable country name.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/iso3166-1-2</t>
+    <t>Deutschland</t>
   </si>
   <si>
     <t>Address.country</t>
   </si>
   <si>
     <t>XAD.6</t>
+  </si>
+  <si>
+    <t>Patient.address:Strassenanschrift.country.id</t>
+  </si>
+  <si>
+    <t>Patient.address.country.id</t>
+  </si>
+  <si>
+    <t>Patient.address:Strassenanschrift.country.extension</t>
+  </si>
+  <si>
+    <t>Patient.address.country.extension</t>
+  </si>
+  <si>
+    <t>value:url}
+value:value.ofType(Coding).system}</t>
+  </si>
+  <si>
+    <t>Patient.address:Strassenanschrift.country.extension:countryCode</t>
+  </si>
+  <si>
+    <t>countryCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {iso21090-codedString}
+</t>
+  </si>
+  <si>
+    <t>Länderkennzeichen nach ISO 3166-1</t>
+  </si>
+  <si>
+    <t>Kodierte Angabe des Länderkennzeichens nach ISO 3166-1.</t>
+  </si>
+  <si>
+    <t>Diese Abbildung entspricht der auf EU-Ebene in Abstimmung befindlichen Profilierung zur [Kodierung der Landesangabe](https://build.fhir.org/ig/hl7-eu/base/StructureDefinition-Address-eu.html).
+Durch die Verwendung der internationalen Kodierung wird die interoperable Verwendung der Adressangabe erleichtert.</t>
+  </si>
+  <si>
+    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
+  &lt;system value="urn:iso:std:iso:3166"/&gt;
+  &lt;code value="DE"/&gt;
+  &lt;display value="Deutschland"/&gt;
+&lt;/valueCoding&gt;</t>
+  </si>
+  <si>
+    <t>Patient.address:Strassenanschrift.country.extension:countryCode.id</t>
+  </si>
+  <si>
+    <t>Patient.address.country.extension.id</t>
+  </si>
+  <si>
+    <t>Patient.address:Strassenanschrift.country.extension:countryCode.extension</t>
+  </si>
+  <si>
+    <t>Patient.address.country.extension.extension</t>
+  </si>
+  <si>
+    <t>Patient.address:Strassenanschrift.country.extension:countryCode.url</t>
+  </si>
+  <si>
+    <t>Patient.address.country.extension.url</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/StructureDefinition/iso21090-codedString</t>
+  </si>
+  <si>
+    <t>Patient.address:Strassenanschrift.country.extension:countryCode.value[x]</t>
+  </si>
+  <si>
+    <t>Patient.address.country.extension.value[x]</t>
+  </si>
+  <si>
+    <t>A coded representation for a string.  Could be codes for country in a country address part, codes for prefixes in a name part, etc.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/iso3166-1-2|4.0.1</t>
+  </si>
+  <si>
+    <t>Patient.address:Strassenanschrift.country.value</t>
+  </si>
+  <si>
+    <t>Patient.address.country.value</t>
   </si>
   <si>
     <t>Patient.address:Strassenanschrift.period</t>
@@ -2638,7 +2729,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM130"/>
+  <dimension ref="A1:AM138"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="76.578125" customWidth="true" bestFit="true"/>
@@ -2660,15 +2751,15 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="34.26953125" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="34.80078125" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="102.66796875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="48.33203125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="29.77734375" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
@@ -6900,7 +6991,7 @@
         <v>79</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>80</v>
+        <v>304</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>114</v>
@@ -6917,7 +7008,7 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>209</v>
@@ -7013,7 +7104,7 @@
         <v>86</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>80</v>
+        <v>304</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>98</v>
@@ -7030,7 +7121,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>220</v>
@@ -7078,7 +7169,7 @@
         <v>80</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>306</v>
+        <v>80</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>80</v>
@@ -7093,7 +7184,7 @@
         <v>80</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>143</v>
+        <v>214</v>
       </c>
       <c r="Y40" t="s" s="2">
         <v>226</v>
@@ -7126,7 +7217,7 @@
         <v>86</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>80</v>
+        <v>304</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>308</v>
@@ -7239,7 +7330,7 @@
         <v>86</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>80</v>
+        <v>304</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>98</v>
@@ -7350,7 +7441,7 @@
         <v>86</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>80</v>
+        <v>304</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>312</v>
@@ -7677,7 +7768,7 @@
         <v>79</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>326</v>
+        <v>304</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>114</v>
@@ -7694,10 +7785,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="B46" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7803,10 +7894,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="B47" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7912,10 +8003,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="B48" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="B48" t="s" s="2">
-        <v>332</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7941,13 +8032,13 @@
         <v>127</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7955,49 +8046,49 @@
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF48" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="S48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF48" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>86</v>
@@ -8023,10 +8114,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="B49" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="B49" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8052,10 +8143,10 @@
         <v>161</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>341</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8067,7 +8158,7 @@
         <v>80</v>
       </c>
       <c r="S49" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="T49" t="s" s="2">
         <v>80</v>
@@ -8086,25 +8177,25 @@
       </c>
       <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF49" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -8130,10 +8221,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="B50" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>346</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8159,10 +8250,10 @@
         <v>100</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8186,34 +8277,34 @@
         <v>80</v>
       </c>
       <c r="W50" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF50" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="X50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -8239,7 +8330,7 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>276</v>
@@ -8273,7 +8364,9 @@
       <c r="M51" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="N51" s="2"/>
+      <c r="N51" t="s" s="2">
+        <v>351</v>
+      </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>80</v>
@@ -8331,10 +8424,10 @@
         <v>86</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>80</v>
+        <v>304</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>98</v>
+        <v>352</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>80</v>
@@ -8348,7 +8441,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>283</v>
@@ -8374,7 +8467,7 @@
         <v>87</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L52" t="s" s="2">
         <v>285</v>
@@ -8442,10 +8535,10 @@
         <v>86</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>80</v>
+        <v>304</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>98</v>
+        <v>355</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>80</v>
@@ -8459,10 +8552,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8568,10 +8661,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8679,10 +8772,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8708,13 +8801,13 @@
         <v>100</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8764,7 +8857,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8773,7 +8866,7 @@
         <v>86</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>98</v>
@@ -8790,10 +8883,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8819,13 +8912,13 @@
         <v>127</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8854,10 +8947,10 @@
         <v>143</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>80</v>
@@ -8875,7 +8968,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8901,10 +8994,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8927,16 +9020,16 @@
         <v>87</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8986,7 +9079,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -9012,10 +9105,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9121,10 +9214,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9215,7 +9308,7 @@
         <v>79</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>80</v>
+        <v>304</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>114</v>
@@ -9232,10 +9325,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9328,7 +9421,7 @@
         <v>86</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>80</v>
+        <v>304</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>98</v>
@@ -9345,10 +9438,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9393,7 +9486,7 @@
         <v>80</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>80</v>
@@ -9414,7 +9507,7 @@
         <v>226</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>307</v>
+        <v>391</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>80</v>
@@ -9441,7 +9534,7 @@
         <v>86</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>80</v>
+        <v>304</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>98</v>
@@ -9458,10 +9551,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9503,7 +9596,7 @@
       </c>
       <c r="Q62" s="2"/>
       <c r="R62" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="S62" t="s" s="2">
         <v>80</v>
@@ -9554,7 +9647,7 @@
         <v>86</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>80</v>
+        <v>304</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>98</v>
@@ -9571,10 +9664,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9665,10 +9758,10 @@
         <v>86</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>80</v>
+        <v>304</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>80</v>
@@ -9682,10 +9775,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9716,7 +9809,9 @@
       <c r="M64" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="N64" s="2"/>
+      <c r="N64" t="s" s="2">
+        <v>351</v>
+      </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>80</v>
@@ -9774,10 +9869,10 @@
         <v>86</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>80</v>
+        <v>304</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>98</v>
+        <v>352</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>80</v>
@@ -9791,10 +9886,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9817,7 +9912,7 @@
         <v>87</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L65" t="s" s="2">
         <v>285</v>
@@ -9885,10 +9980,10 @@
         <v>86</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>80</v>
+        <v>304</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>98</v>
+        <v>355</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>80</v>
@@ -9902,10 +9997,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9931,13 +10026,13 @@
         <v>100</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9987,7 +10082,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -10013,10 +10108,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10039,70 +10134,70 @@
         <v>87</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="M67" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="P67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q67" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="R67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF67" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="P67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q67" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="R67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -10117,7 +10212,7 @@
         <v>98</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>80</v>
@@ -10128,10 +10223,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10154,19 +10249,19 @@
         <v>87</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>80</v>
@@ -10215,7 +10310,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10233,7 +10328,7 @@
         <v>80</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>80</v>
@@ -10241,10 +10336,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10267,19 +10362,19 @@
         <v>87</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>80</v>
@@ -10328,7 +10423,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10346,7 +10441,7 @@
         <v>80</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>80</v>
@@ -10354,10 +10449,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10383,16 +10478,16 @@
         <v>161</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>80</v>
@@ -10420,10 +10515,10 @@
         <v>214</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>80</v>
@@ -10441,7 +10536,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10459,7 +10554,7 @@
         <v>80</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>80</v>
@@ -10467,10 +10562,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10576,10 +10671,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10683,13 +10778,13 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="D73" t="s" s="2">
         <v>80</v>
@@ -10711,13 +10806,13 @@
         <v>80</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10777,7 +10872,7 @@
         <v>79</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>326</v>
+        <v>304</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>114</v>
@@ -10794,10 +10889,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10823,10 +10918,10 @@
         <v>100</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10877,7 +10972,7 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10903,10 +10998,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10929,19 +11024,19 @@
         <v>87</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>80</v>
@@ -10990,7 +11085,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -11008,18 +11103,18 @@
         <v>80</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11042,19 +11137,19 @@
         <v>87</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>80</v>
@@ -11103,7 +11198,7 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -11121,7 +11216,7 @@
         <v>80</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>80</v>
@@ -11129,10 +11224,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11155,19 +11250,19 @@
         <v>87</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>80</v>
@@ -11214,7 +11309,7 @@
         <v>112</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -11232,7 +11327,7 @@
         <v>80</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>80</v>
@@ -11240,13 +11335,13 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="D78" t="s" s="2">
         <v>80</v>
@@ -11268,19 +11363,19 @@
         <v>87</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>80</v>
@@ -11290,7 +11385,7 @@
         <v>80</v>
       </c>
       <c r="S78" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="T78" t="s" s="2">
         <v>80</v>
@@ -11329,7 +11424,7 @@
         <v>80</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11341,13 +11436,13 @@
         <v>80</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>80</v>
@@ -11355,10 +11450,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11464,10 +11559,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11558,7 +11653,7 @@
         <v>79</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>80</v>
+        <v>304</v>
       </c>
       <c r="AJ80" t="s" s="2">
         <v>114</v>
@@ -11575,13 +11670,13 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="D81" t="s" s="2">
         <v>105</v>
@@ -11603,13 +11698,13 @@
         <v>80</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="N81" t="s" s="2">
         <v>109</v>
@@ -11671,7 +11766,7 @@
         <v>79</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>326</v>
+        <v>304</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>114</v>
@@ -11688,10 +11783,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11717,16 +11812,16 @@
         <v>161</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>80</v>
@@ -11739,7 +11834,7 @@
         <v>80</v>
       </c>
       <c r="T82" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="U82" t="s" s="2">
         <v>80</v>
@@ -11754,10 +11849,10 @@
         <v>214</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>80</v>
@@ -11775,7 +11870,7 @@
         <v>80</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -11784,7 +11879,7 @@
         <v>86</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>80</v>
+        <v>304</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>98</v>
@@ -11793,7 +11888,7 @@
         <v>80</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>80</v>
@@ -11801,10 +11896,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11830,13 +11925,13 @@
         <v>161</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -11850,7 +11945,7 @@
         <v>80</v>
       </c>
       <c r="T83" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="U83" t="s" s="2">
         <v>80</v>
@@ -11865,10 +11960,10 @@
         <v>214</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>80</v>
@@ -11886,7 +11981,7 @@
         <v>80</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -11895,7 +11990,7 @@
         <v>86</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>80</v>
+        <v>304</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>98</v>
@@ -11904,7 +11999,7 @@
         <v>80</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>80</v>
@@ -11912,10 +12007,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11941,16 +12036,16 @@
         <v>100</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>80</v>
@@ -11963,7 +12058,7 @@
         <v>80</v>
       </c>
       <c r="T84" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="U84" t="s" s="2">
         <v>80</v>
@@ -11999,7 +12094,7 @@
         <v>80</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -12008,7 +12103,7 @@
         <v>86</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>80</v>
+        <v>304</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>98</v>
@@ -12017,7 +12112,7 @@
         <v>80</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>80</v>
@@ -12025,10 +12120,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12039,7 +12134,7 @@
         <v>78</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>80</v>
@@ -12054,12 +12149,14 @@
         <v>100</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="N85" s="2"/>
+        <v>519</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>520</v>
+      </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>80</v>
@@ -12072,7 +12169,7 @@
         <v>80</v>
       </c>
       <c r="T85" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="U85" t="s" s="2">
         <v>80</v>
@@ -12108,7 +12205,7 @@
         <v>80</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -12117,7 +12214,7 @@
         <v>79</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>80</v>
+        <v>304</v>
       </c>
       <c r="AJ85" t="s" s="2">
         <v>98</v>
@@ -12126,7 +12223,7 @@
         <v>80</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>80</v>
@@ -12134,10 +12231,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12163,10 +12260,10 @@
         <v>100</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>315</v>
+        <v>101</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>316</v>
+        <v>102</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12243,10 +12340,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12275,7 +12372,7 @@
         <v>107</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>184</v>
+        <v>108</v>
       </c>
       <c r="N87" t="s" s="2">
         <v>109</v>
@@ -12318,7 +12415,9 @@
       <c r="AB87" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="AC87" s="2"/>
+      <c r="AC87" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="AD87" t="s" s="2">
         <v>80</v>
       </c>
@@ -12335,7 +12434,7 @@
         <v>79</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>80</v>
+        <v>304</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>114</v>
@@ -12352,13 +12451,13 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="D88" t="s" s="2">
         <v>105</v>
@@ -12380,13 +12479,13 @@
         <v>80</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="N88" t="s" s="2">
         <v>109</v>
@@ -12448,7 +12547,7 @@
         <v>79</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>326</v>
+        <v>304</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>114</v>
@@ -12465,13 +12564,13 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="D89" t="s" s="2">
         <v>105</v>
@@ -12493,13 +12592,13 @@
         <v>80</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="N89" t="s" s="2">
         <v>109</v>
@@ -12561,7 +12660,7 @@
         <v>79</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>326</v>
+        <v>304</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>114</v>
@@ -12578,13 +12677,13 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="D90" t="s" s="2">
         <v>105</v>
@@ -12606,13 +12705,13 @@
         <v>80</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="N90" t="s" s="2">
         <v>109</v>
@@ -12674,7 +12773,7 @@
         <v>79</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>326</v>
+        <v>304</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>114</v>
@@ -12691,13 +12790,13 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="D91" t="s" s="2">
         <v>105</v>
@@ -12719,13 +12818,13 @@
         <v>80</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="N91" t="s" s="2">
         <v>109</v>
@@ -12787,7 +12886,7 @@
         <v>79</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>326</v>
+        <v>304</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>114</v>
@@ -12804,10 +12903,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12833,10 +12932,10 @@
         <v>100</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -12860,34 +12959,34 @@
         <v>80</v>
       </c>
       <c r="W92" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF92" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="X92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF92" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -12913,14 +13012,14 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -12942,12 +13041,14 @@
         <v>100</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="N93" s="2"/>
+        <v>551</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>520</v>
+      </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>80</v>
@@ -12960,7 +13061,7 @@
         <v>80</v>
       </c>
       <c r="T93" t="s" s="2">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="U93" t="s" s="2">
         <v>80</v>
@@ -12996,7 +13097,7 @@
         <v>80</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -13005,7 +13106,7 @@
         <v>86</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>80</v>
+        <v>304</v>
       </c>
       <c r="AJ93" t="s" s="2">
         <v>98</v>
@@ -13014,7 +13115,7 @@
         <v>80</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>80</v>
@@ -13022,10 +13123,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13131,10 +13232,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13238,13 +13339,13 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="D96" t="s" s="2">
         <v>80</v>
@@ -13266,13 +13367,13 @@
         <v>80</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13332,7 +13433,7 @@
         <v>79</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>326</v>
+        <v>304</v>
       </c>
       <c r="AJ96" t="s" s="2">
         <v>114</v>
@@ -13349,10 +13450,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13378,10 +13479,10 @@
         <v>100</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="M97" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -13405,34 +13506,34 @@
         <v>80</v>
       </c>
       <c r="W97" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="X97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF97" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="X97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF97" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -13458,14 +13559,14 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
@@ -13487,13 +13588,13 @@
         <v>100</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -13507,7 +13608,7 @@
         <v>80</v>
       </c>
       <c r="T98" t="s" s="2">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="U98" t="s" s="2">
         <v>80</v>
@@ -13543,7 +13644,7 @@
         <v>80</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>
@@ -13552,7 +13653,7 @@
         <v>86</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>80</v>
+        <v>304</v>
       </c>
       <c r="AJ98" t="s" s="2">
         <v>98</v>
@@ -13561,7 +13662,7 @@
         <v>80</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>80</v>
@@ -13569,14 +13670,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -13598,12 +13699,14 @@
         <v>100</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="N99" s="2"/>
+        <v>579</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>520</v>
+      </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>80</v>
@@ -13632,7 +13735,7 @@
       </c>
       <c r="Y99" s="2"/>
       <c r="Z99" t="s" s="2">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>80</v>
@@ -13650,7 +13753,7 @@
         <v>80</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
@@ -13659,7 +13762,7 @@
         <v>86</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>80</v>
+        <v>304</v>
       </c>
       <c r="AJ99" t="s" s="2">
         <v>98</v>
@@ -13668,7 +13771,7 @@
         <v>80</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>80</v>
@@ -13676,14 +13779,14 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
@@ -13705,12 +13808,14 @@
         <v>100</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="N100" s="2"/>
+        <v>587</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>520</v>
+      </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>80</v>
@@ -13723,7 +13828,7 @@
         <v>80</v>
       </c>
       <c r="T100" t="s" s="2">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="U100" t="s" s="2">
         <v>80</v>
@@ -13759,7 +13864,7 @@
         <v>80</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -13768,7 +13873,7 @@
         <v>86</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>80</v>
+        <v>304</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>98</v>
@@ -13777,7 +13882,7 @@
         <v>80</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>80</v>
@@ -13785,10 +13890,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13814,13 +13919,13 @@
         <v>100</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -13834,7 +13939,7 @@
         <v>80</v>
       </c>
       <c r="T101" t="s" s="2">
-        <v>80</v>
+        <v>596</v>
       </c>
       <c r="U101" t="s" s="2">
         <v>80</v>
@@ -13846,11 +13951,13 @@
         <v>80</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="Y101" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z101" t="s" s="2">
-        <v>592</v>
+        <v>80</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>80</v>
@@ -13868,7 +13975,7 @@
         <v>80</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -13877,7 +13984,7 @@
         <v>86</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>80</v>
+        <v>304</v>
       </c>
       <c r="AJ101" t="s" s="2">
         <v>98</v>
@@ -13886,7 +13993,7 @@
         <v>80</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>80</v>
@@ -13894,10 +14001,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13917,21 +14024,19 @@
         <v>80</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>277</v>
+        <v>100</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>597</v>
+        <v>101</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>598</v>
+        <v>102</v>
       </c>
       <c r="N102" s="2"/>
-      <c r="O102" t="s" s="2">
-        <v>599</v>
-      </c>
+      <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>80</v>
       </c>
@@ -13943,7 +14048,7 @@
         <v>80</v>
       </c>
       <c r="T102" t="s" s="2">
-        <v>600</v>
+        <v>80</v>
       </c>
       <c r="U102" t="s" s="2">
         <v>80</v>
@@ -13979,7 +14084,7 @@
         <v>80</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>601</v>
+        <v>103</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -13991,13 +14096,13 @@
         <v>80</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>602</v>
+        <v>80</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>80</v>
@@ -14005,21 +14110,21 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>80</v>
@@ -14031,18 +14136,18 @@
         <v>80</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>221</v>
+        <v>106</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>604</v>
+        <v>107</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="N103" s="2"/>
-      <c r="O103" t="s" s="2">
-        <v>606</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>80</v>
       </c>
@@ -14066,49 +14171,49 @@
         <v>80</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>143</v>
+        <v>80</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>607</v>
+        <v>80</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>608</v>
+        <v>80</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB103" t="s" s="2">
-        <v>80</v>
+        <v>603</v>
       </c>
       <c r="AC103" t="s" s="2">
-        <v>80</v>
+        <v>111</v>
       </c>
       <c r="AD103" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE103" t="s" s="2">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>603</v>
+        <v>113</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>80</v>
+        <v>304</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>609</v>
+        <v>80</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>80</v>
@@ -14116,14 +14221,16 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="C104" s="2"/>
+        <v>602</v>
+      </c>
+      <c r="C104" t="s" s="2">
+        <v>605</v>
+      </c>
       <c r="D104" t="s" s="2">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -14142,20 +14249,18 @@
         <v>80</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>615</v>
-      </c>
+        <v>609</v>
+      </c>
+      <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>80</v>
       </c>
@@ -14167,7 +14272,7 @@
         <v>80</v>
       </c>
       <c r="T104" t="s" s="2">
-        <v>80</v>
+        <v>610</v>
       </c>
       <c r="U104" t="s" s="2">
         <v>80</v>
@@ -14203,25 +14308,25 @@
         <v>80</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>610</v>
+        <v>113</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>80</v>
+        <v>304</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>616</v>
+        <v>80</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>80</v>
@@ -14229,10 +14334,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14243,7 +14348,7 @@
         <v>78</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>80</v>
@@ -14255,20 +14360,16 @@
         <v>80</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>618</v>
+        <v>100</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>619</v>
+        <v>101</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="O105" t="s" s="2">
-        <v>622</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N105" s="2"/>
+      <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
         <v>80</v>
       </c>
@@ -14316,25 +14417,25 @@
         <v>80</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>617</v>
+        <v>103</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>623</v>
+        <v>80</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>80</v>
@@ -14342,21 +14443,21 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>624</v>
+        <v>613</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>624</v>
+        <v>614</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>80</v>
@@ -14368,20 +14469,18 @@
         <v>80</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>625</v>
+        <v>106</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>626</v>
+        <v>107</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>627</v>
+        <v>108</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="O106" t="s" s="2">
-        <v>629</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
         <v>80</v>
       </c>
@@ -14417,19 +14516,19 @@
         <v>80</v>
       </c>
       <c r="AB106" t="s" s="2">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="AC106" t="s" s="2">
-        <v>80</v>
+        <v>111</v>
       </c>
       <c r="AD106" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE106" t="s" s="2">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>624</v>
+        <v>113</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
@@ -14438,10 +14537,10 @@
         <v>79</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>80</v>
+        <v>304</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>630</v>
+        <v>114</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>80</v>
@@ -14455,10 +14554,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>631</v>
+        <v>615</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14466,7 +14565,7 @@
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="G107" t="s" s="2">
         <v>86</v>
@@ -14481,22 +14580,24 @@
         <v>80</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>101</v>
+        <v>332</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N107" s="2"/>
+        <v>333</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>334</v>
+      </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q107" s="2"/>
       <c r="R107" t="s" s="2">
-        <v>80</v>
+        <v>617</v>
       </c>
       <c r="S107" t="s" s="2">
         <v>80</v>
@@ -14538,10 +14639,10 @@
         <v>80</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>103</v>
+        <v>336</v>
       </c>
       <c r="AG107" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AH107" t="s" s="2">
         <v>86</v>
@@ -14564,21 +14665,21 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>632</v>
+        <v>618</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>632</v>
+        <v>619</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H108" t="s" s="2">
         <v>80</v>
@@ -14590,17 +14691,15 @@
         <v>80</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>106</v>
+        <v>139</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>107</v>
+        <v>339</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>340</v>
+      </c>
+      <c r="N108" s="2"/>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>80</v>
@@ -14625,13 +14724,13 @@
         <v>80</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>80</v>
+        <v>214</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>80</v>
+        <v>620</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>80</v>
+        <v>621</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>80</v>
@@ -14649,19 +14748,19 @@
         <v>80</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>113</v>
+        <v>343</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>80</v>
+        <v>304</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>80</v>
@@ -14675,46 +14774,42 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>633</v>
+        <v>622</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>633</v>
+        <v>623</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>634</v>
+        <v>80</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I109" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>635</v>
+        <v>346</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="O109" t="s" s="2">
-        <v>189</v>
-      </c>
+        <v>346</v>
+      </c>
+      <c r="N109" s="2"/>
+      <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>80</v>
       </c>
@@ -14735,7 +14830,7 @@
         <v>80</v>
       </c>
       <c r="W109" t="s" s="2">
-        <v>80</v>
+        <v>348</v>
       </c>
       <c r="X109" t="s" s="2">
         <v>80</v>
@@ -14762,19 +14857,19 @@
         <v>80</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>637</v>
+        <v>349</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>80</v>
@@ -14788,10 +14883,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>638</v>
+        <v>624</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>638</v>
+        <v>625</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14802,7 +14897,7 @@
         <v>78</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>80</v>
@@ -14811,20 +14906,22 @@
         <v>80</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>221</v>
+        <v>277</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>639</v>
+        <v>626</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="N110" s="2"/>
+        <v>627</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>351</v>
+      </c>
       <c r="O110" t="s" s="2">
-        <v>641</v>
+        <v>628</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>80</v>
@@ -14837,7 +14934,7 @@
         <v>80</v>
       </c>
       <c r="T110" t="s" s="2">
-        <v>80</v>
+        <v>629</v>
       </c>
       <c r="U110" t="s" s="2">
         <v>80</v>
@@ -14849,13 +14946,13 @@
         <v>80</v>
       </c>
       <c r="X110" t="s" s="2">
-        <v>143</v>
+        <v>80</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>642</v>
+        <v>80</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>643</v>
+        <v>80</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>80</v>
@@ -14873,25 +14970,25 @@
         <v>80</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AI110" t="s" s="2">
-        <v>80</v>
+        <v>304</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>98</v>
+        <v>352</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>644</v>
+        <v>631</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>80</v>
@@ -14899,10 +14996,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>645</v>
+        <v>632</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>645</v>
+        <v>632</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14925,17 +15022,17 @@
         <v>80</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>414</v>
+        <v>221</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>646</v>
+        <v>633</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>647</v>
+        <v>634</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" t="s" s="2">
-        <v>648</v>
+        <v>635</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>80</v>
@@ -14960,13 +15057,13 @@
         <v>80</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>80</v>
+        <v>143</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>80</v>
+        <v>636</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>80</v>
+        <v>637</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>80</v>
@@ -14984,7 +15081,7 @@
         <v>80</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>645</v>
+        <v>632</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
@@ -15002,7 +15099,7 @@
         <v>80</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>649</v>
+        <v>638</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>80</v>
@@ -15010,10 +15107,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>650</v>
+        <v>639</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>650</v>
+        <v>639</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15024,7 +15121,7 @@
         <v>78</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H112" t="s" s="2">
         <v>80</v>
@@ -15036,19 +15133,19 @@
         <v>80</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>421</v>
+        <v>640</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>651</v>
+        <v>641</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>652</v>
+        <v>642</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>653</v>
+        <v>643</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>425</v>
+        <v>644</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>80</v>
@@ -15097,13 +15194,13 @@
         <v>80</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>650</v>
+        <v>639</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>80</v>
@@ -15115,7 +15212,7 @@
         <v>80</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>654</v>
+        <v>645</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>80</v>
@@ -15123,10 +15220,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>655</v>
+        <v>646</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>655</v>
+        <v>646</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15137,7 +15234,7 @@
         <v>78</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>80</v>
@@ -15149,17 +15246,19 @@
         <v>80</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>460</v>
+        <v>647</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>656</v>
+        <v>648</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="N113" s="2"/>
+        <v>649</v>
+      </c>
+      <c r="N113" t="s" s="2">
+        <v>650</v>
+      </c>
       <c r="O113" t="s" s="2">
-        <v>658</v>
+        <v>651</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>80</v>
@@ -15208,13 +15307,13 @@
         <v>80</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>655</v>
+        <v>646</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>80</v>
@@ -15226,7 +15325,7 @@
         <v>80</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>659</v>
+        <v>652</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>80</v>
@@ -15234,10 +15333,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>660</v>
+        <v>653</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>660</v>
+        <v>653</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15248,7 +15347,7 @@
         <v>78</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>80</v>
@@ -15260,17 +15359,19 @@
         <v>80</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>161</v>
+        <v>654</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="N114" s="2"/>
+        <v>656</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>657</v>
+      </c>
       <c r="O114" t="s" s="2">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>80</v>
@@ -15295,13 +15396,13 @@
         <v>80</v>
       </c>
       <c r="X114" t="s" s="2">
-        <v>214</v>
+        <v>80</v>
       </c>
       <c r="Y114" t="s" s="2">
-        <v>432</v>
+        <v>80</v>
       </c>
       <c r="Z114" t="s" s="2">
-        <v>433</v>
+        <v>80</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>80</v>
@@ -15319,25 +15420,25 @@
         <v>80</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>660</v>
+        <v>653</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>98</v>
+        <v>659</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>664</v>
+        <v>80</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>80</v>
@@ -15345,10 +15446,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15371,18 +15472,16 @@
         <v>80</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>284</v>
+        <v>100</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>666</v>
+        <v>101</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>667</v>
+        <v>102</v>
       </c>
       <c r="N115" s="2"/>
-      <c r="O115" t="s" s="2">
-        <v>668</v>
-      </c>
+      <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
         <v>80</v>
       </c>
@@ -15430,7 +15529,7 @@
         <v>80</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>665</v>
+        <v>103</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>78</v>
@@ -15439,16 +15538,16 @@
         <v>86</v>
       </c>
       <c r="AI115" t="s" s="2">
-        <v>669</v>
+        <v>80</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>670</v>
+        <v>80</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>80</v>
@@ -15456,21 +15555,21 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>671</v>
+        <v>661</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>671</v>
+        <v>661</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>80</v>
@@ -15482,15 +15581,17 @@
         <v>80</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>277</v>
+        <v>106</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>672</v>
+        <v>107</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>673</v>
-      </c>
-      <c r="N116" s="2"/>
+        <v>108</v>
+      </c>
+      <c r="N116" t="s" s="2">
+        <v>109</v>
+      </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
         <v>80</v>
@@ -15539,19 +15640,19 @@
         <v>80</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>671</v>
+        <v>113</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AI116" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AK116" t="s" s="2">
         <v>80</v>
@@ -15565,14 +15666,14 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>674</v>
+        <v>662</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>674</v>
+        <v>662</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>80</v>
+        <v>663</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
@@ -15585,25 +15686,25 @@
         <v>80</v>
       </c>
       <c r="I117" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="J117" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>625</v>
+        <v>106</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>675</v>
+        <v>664</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>676</v>
+        <v>665</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>677</v>
+        <v>109</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>678</v>
+        <v>189</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>80</v>
@@ -15652,7 +15753,7 @@
         <v>80</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>674</v>
+        <v>666</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>78</v>
@@ -15664,7 +15765,7 @@
         <v>80</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>80</v>
@@ -15678,10 +15779,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>679</v>
+        <v>667</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>679</v>
+        <v>667</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15692,7 +15793,7 @@
         <v>78</v>
       </c>
       <c r="G118" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H118" t="s" s="2">
         <v>80</v>
@@ -15704,16 +15805,18 @@
         <v>80</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>100</v>
+        <v>221</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>101</v>
+        <v>668</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>102</v>
+        <v>669</v>
       </c>
       <c r="N118" s="2"/>
-      <c r="O118" s="2"/>
+      <c r="O118" t="s" s="2">
+        <v>670</v>
+      </c>
       <c r="P118" t="s" s="2">
         <v>80</v>
       </c>
@@ -15737,13 +15840,13 @@
         <v>80</v>
       </c>
       <c r="X118" t="s" s="2">
-        <v>80</v>
+        <v>143</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>80</v>
+        <v>671</v>
       </c>
       <c r="Z118" t="s" s="2">
-        <v>80</v>
+        <v>672</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>80</v>
@@ -15761,25 +15864,25 @@
         <v>80</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>103</v>
+        <v>667</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AI118" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>80</v>
+        <v>673</v>
       </c>
       <c r="AM118" t="s" s="2">
         <v>80</v>
@@ -15787,21 +15890,21 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H119" t="s" s="2">
         <v>80</v>
@@ -15813,18 +15916,18 @@
         <v>80</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>106</v>
+        <v>417</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>107</v>
+        <v>675</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="O119" s="2"/>
+        <v>676</v>
+      </c>
+      <c r="N119" s="2"/>
+      <c r="O119" t="s" s="2">
+        <v>677</v>
+      </c>
       <c r="P119" t="s" s="2">
         <v>80</v>
       </c>
@@ -15872,25 +15975,25 @@
         <v>80</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>113</v>
+        <v>674</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AI119" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="AK119" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>80</v>
+        <v>678</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>80</v>
@@ -15898,14 +16001,14 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>634</v>
+        <v>80</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
@@ -15918,25 +16021,25 @@
         <v>80</v>
       </c>
       <c r="I120" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="J120" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>106</v>
+        <v>424</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>635</v>
+        <v>680</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>636</v>
+        <v>681</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>109</v>
+        <v>682</v>
       </c>
       <c r="O120" t="s" s="2">
-        <v>189</v>
+        <v>428</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>80</v>
@@ -15985,7 +16088,7 @@
         <v>80</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>637</v>
+        <v>679</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>78</v>
@@ -15997,13 +16100,13 @@
         <v>80</v>
       </c>
       <c r="AJ120" t="s" s="2">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="AK120" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>80</v>
+        <v>683</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>80</v>
@@ -16011,10 +16114,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16022,7 +16125,7 @@
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="G121" t="s" s="2">
         <v>86</v>
@@ -16037,19 +16140,17 @@
         <v>80</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>221</v>
+        <v>463</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>684</v>
-      </c>
-      <c r="N121" t="s" s="2">
-        <v>685</v>
-      </c>
+        <v>686</v>
+      </c>
+      <c r="N121" s="2"/>
       <c r="O121" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>80</v>
@@ -16074,13 +16175,13 @@
         <v>80</v>
       </c>
       <c r="X121" t="s" s="2">
-        <v>165</v>
+        <v>80</v>
       </c>
       <c r="Y121" t="s" s="2">
-        <v>166</v>
+        <v>80</v>
       </c>
       <c r="Z121" t="s" s="2">
-        <v>167</v>
+        <v>80</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>80</v>
@@ -16098,10 +16199,10 @@
         <v>80</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="AG121" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AH121" t="s" s="2">
         <v>86</v>
@@ -16116,7 +16217,7 @@
         <v>80</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>80</v>
@@ -16124,10 +16225,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16150,17 +16251,15 @@
         <v>80</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>406</v>
+        <v>161</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>690</v>
-      </c>
-      <c r="N122" t="s" s="2">
         <v>691</v>
       </c>
+      <c r="N122" s="2"/>
       <c r="O122" t="s" s="2">
         <v>692</v>
       </c>
@@ -16187,13 +16286,13 @@
         <v>80</v>
       </c>
       <c r="X122" t="s" s="2">
-        <v>80</v>
+        <v>214</v>
       </c>
       <c r="Y122" t="s" s="2">
-        <v>80</v>
+        <v>435</v>
       </c>
       <c r="Z122" t="s" s="2">
-        <v>80</v>
+        <v>436</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>80</v>
@@ -16211,7 +16310,7 @@
         <v>80</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>78</v>
@@ -16244,14 +16343,14 @@
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
-        <v>695</v>
+        <v>80</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H123" t="s" s="2">
         <v>80</v>
@@ -16263,18 +16362,18 @@
         <v>80</v>
       </c>
       <c r="K123" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="L123" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="M123" t="s" s="2">
         <v>696</v>
       </c>
-      <c r="L123" t="s" s="2">
+      <c r="N123" s="2"/>
+      <c r="O123" t="s" s="2">
         <v>697</v>
       </c>
-      <c r="M123" t="s" s="2">
-        <v>698</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>699</v>
-      </c>
-      <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
         <v>80</v>
       </c>
@@ -16328,10 +16427,10 @@
         <v>78</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AI123" t="s" s="2">
-        <v>80</v>
+        <v>698</v>
       </c>
       <c r="AJ123" t="s" s="2">
         <v>98</v>
@@ -16340,7 +16439,7 @@
         <v>80</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="AM123" t="s" s="2">
         <v>80</v>
@@ -16348,10 +16447,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16371,23 +16470,19 @@
         <v>80</v>
       </c>
       <c r="J124" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="L124" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="M124" t="s" s="2">
         <v>702</v>
       </c>
-      <c r="M124" t="s" s="2">
-        <v>703</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>704</v>
-      </c>
-      <c r="O124" t="s" s="2">
-        <v>705</v>
-      </c>
+      <c r="N124" s="2"/>
+      <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
         <v>80</v>
       </c>
@@ -16435,7 +16530,7 @@
         <v>80</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>78</v>
@@ -16461,10 +16556,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16481,25 +16576,25 @@
         <v>80</v>
       </c>
       <c r="I125" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="J125" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>625</v>
+        <v>654</v>
       </c>
       <c r="L125" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="M125" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="N125" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="O125" t="s" s="2">
         <v>707</v>
-      </c>
-      <c r="M125" t="s" s="2">
-        <v>708</v>
-      </c>
-      <c r="N125" t="s" s="2">
-        <v>709</v>
-      </c>
-      <c r="O125" t="s" s="2">
-        <v>710</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>80</v>
@@ -16548,7 +16643,7 @@
         <v>80</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>78</v>
@@ -16574,10 +16669,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16683,10 +16778,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16794,14 +16889,14 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>634</v>
+        <v>663</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
@@ -16823,10 +16918,10 @@
         <v>106</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>635</v>
+        <v>664</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>636</v>
+        <v>665</v>
       </c>
       <c r="N128" t="s" s="2">
         <v>109</v>
@@ -16881,7 +16976,7 @@
         <v>80</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>637</v>
+        <v>666</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>78</v>
@@ -16907,10 +17002,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -16930,21 +17025,23 @@
         <v>80</v>
       </c>
       <c r="J129" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="K129" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="L129" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="M129" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="N129" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="O129" t="s" s="2">
         <v>715</v>
       </c>
-      <c r="L129" t="s" s="2">
-        <v>716</v>
-      </c>
-      <c r="M129" t="s" s="2">
-        <v>717</v>
-      </c>
-      <c r="N129" t="s" s="2">
-        <v>718</v>
-      </c>
-      <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
         <v>80</v>
       </c>
@@ -16968,13 +17065,13 @@
         <v>80</v>
       </c>
       <c r="X129" t="s" s="2">
-        <v>80</v>
+        <v>165</v>
       </c>
       <c r="Y129" t="s" s="2">
-        <v>80</v>
+        <v>166</v>
       </c>
       <c r="Z129" t="s" s="2">
-        <v>80</v>
+        <v>167</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>80</v>
@@ -16992,7 +17089,7 @@
         <v>80</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>86</v>
@@ -17010,7 +17107,7 @@
         <v>80</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="AM129" t="s" s="2">
         <v>80</v>
@@ -17018,10 +17115,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17029,7 +17126,7 @@
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="G130" t="s" s="2">
         <v>86</v>
@@ -17041,19 +17138,23 @@
         <v>80</v>
       </c>
       <c r="J130" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>161</v>
+        <v>409</v>
       </c>
       <c r="L130" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="M130" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="N130" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="O130" t="s" s="2">
         <v>721</v>
       </c>
-      <c r="M130" t="s" s="2">
-        <v>722</v>
-      </c>
-      <c r="N130" s="2"/>
-      <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
         <v>80</v>
       </c>
@@ -17077,13 +17178,13 @@
         <v>80</v>
       </c>
       <c r="X130" t="s" s="2">
-        <v>214</v>
+        <v>80</v>
       </c>
       <c r="Y130" t="s" s="2">
-        <v>722</v>
+        <v>80</v>
       </c>
       <c r="Z130" t="s" s="2">
-        <v>723</v>
+        <v>80</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>80</v>
@@ -17101,10 +17202,10 @@
         <v>80</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="AG130" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AH130" t="s" s="2">
         <v>86</v>
@@ -17119,14 +17220,904 @@
         <v>80</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>80</v>
+        <v>722</v>
       </c>
       <c r="AM130" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="131" hidden="true">
+      <c r="A131" t="s" s="2">
+        <v>723</v>
+      </c>
+      <c r="B131" t="s" s="2">
+        <v>723</v>
+      </c>
+      <c r="C131" s="2"/>
+      <c r="D131" t="s" s="2">
+        <v>724</v>
+      </c>
+      <c r="E131" s="2"/>
+      <c r="F131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G131" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K131" t="s" s="2">
+        <v>725</v>
+      </c>
+      <c r="L131" t="s" s="2">
+        <v>726</v>
+      </c>
+      <c r="M131" t="s" s="2">
+        <v>727</v>
+      </c>
+      <c r="N131" t="s" s="2">
+        <v>728</v>
+      </c>
+      <c r="O131" s="2"/>
+      <c r="P131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q131" s="2"/>
+      <c r="R131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF131" t="s" s="2">
+        <v>723</v>
+      </c>
+      <c r="AG131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH131" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ131" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL131" t="s" s="2">
+        <v>729</v>
+      </c>
+      <c r="AM131" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="132" hidden="true">
+      <c r="A132" t="s" s="2">
+        <v>730</v>
+      </c>
+      <c r="B132" t="s" s="2">
+        <v>730</v>
+      </c>
+      <c r="C132" s="2"/>
+      <c r="D132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E132" s="2"/>
+      <c r="F132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G132" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J132" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K132" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="L132" t="s" s="2">
+        <v>731</v>
+      </c>
+      <c r="M132" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="N132" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="O132" t="s" s="2">
+        <v>734</v>
+      </c>
+      <c r="P132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q132" s="2"/>
+      <c r="R132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF132" t="s" s="2">
+        <v>730</v>
+      </c>
+      <c r="AG132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH132" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ132" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM132" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="133" hidden="true">
+      <c r="A133" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="B133" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="C133" s="2"/>
+      <c r="D133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E133" s="2"/>
+      <c r="F133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G133" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I133" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="J133" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K133" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="L133" t="s" s="2">
+        <v>736</v>
+      </c>
+      <c r="M133" t="s" s="2">
+        <v>737</v>
+      </c>
+      <c r="N133" t="s" s="2">
+        <v>738</v>
+      </c>
+      <c r="O133" t="s" s="2">
+        <v>739</v>
+      </c>
+      <c r="P133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q133" s="2"/>
+      <c r="R133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF133" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="AG133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH133" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ133" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM133" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="134" hidden="true">
+      <c r="A134" t="s" s="2">
+        <v>740</v>
+      </c>
+      <c r="B134" t="s" s="2">
+        <v>740</v>
+      </c>
+      <c r="C134" s="2"/>
+      <c r="D134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E134" s="2"/>
+      <c r="F134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G134" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K134" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="L134" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="M134" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="N134" s="2"/>
+      <c r="O134" s="2"/>
+      <c r="P134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q134" s="2"/>
+      <c r="R134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF134" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AG134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH134" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM134" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="135" hidden="true">
+      <c r="A135" t="s" s="2">
+        <v>741</v>
+      </c>
+      <c r="B135" t="s" s="2">
+        <v>741</v>
+      </c>
+      <c r="C135" s="2"/>
+      <c r="D135" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="E135" s="2"/>
+      <c r="F135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G135" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K135" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L135" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="M135" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="N135" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="O135" s="2"/>
+      <c r="P135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q135" s="2"/>
+      <c r="R135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF135" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AG135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH135" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ135" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AK135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM135" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="136" hidden="true">
+      <c r="A136" t="s" s="2">
+        <v>742</v>
+      </c>
+      <c r="B136" t="s" s="2">
+        <v>742</v>
+      </c>
+      <c r="C136" s="2"/>
+      <c r="D136" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="E136" s="2"/>
+      <c r="F136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G136" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I136" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="J136" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K136" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L136" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="M136" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="N136" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="O136" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="P136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q136" s="2"/>
+      <c r="R136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF136" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="AG136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH136" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ136" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AK136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM136" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="137" hidden="true">
+      <c r="A137" t="s" s="2">
+        <v>743</v>
+      </c>
+      <c r="B137" t="s" s="2">
+        <v>743</v>
+      </c>
+      <c r="C137" s="2"/>
+      <c r="D137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E137" s="2"/>
+      <c r="F137" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G137" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J137" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K137" t="s" s="2">
+        <v>744</v>
+      </c>
+      <c r="L137" t="s" s="2">
+        <v>745</v>
+      </c>
+      <c r="M137" t="s" s="2">
+        <v>746</v>
+      </c>
+      <c r="N137" t="s" s="2">
+        <v>747</v>
+      </c>
+      <c r="O137" s="2"/>
+      <c r="P137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q137" s="2"/>
+      <c r="R137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF137" t="s" s="2">
+        <v>743</v>
+      </c>
+      <c r="AG137" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AH137" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ137" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL137" t="s" s="2">
+        <v>748</v>
+      </c>
+      <c r="AM137" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="138" hidden="true">
+      <c r="A138" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="B138" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="C138" s="2"/>
+      <c r="D138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E138" s="2"/>
+      <c r="F138" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G138" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J138" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K138" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="L138" t="s" s="2">
+        <v>750</v>
+      </c>
+      <c r="M138" t="s" s="2">
+        <v>751</v>
+      </c>
+      <c r="N138" s="2"/>
+      <c r="O138" s="2"/>
+      <c r="P138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q138" s="2"/>
+      <c r="R138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X138" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y138" t="s" s="2">
+        <v>751</v>
+      </c>
+      <c r="Z138" t="s" s="2">
+        <v>752</v>
+      </c>
+      <c r="AA138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF138" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="AG138" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AH138" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ138" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM138" t="s" s="2">
         <v>80</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AM130">
+  <autoFilter ref="A1:AM138">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -17136,7 +18127,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI129">
+  <conditionalFormatting sqref="A2:AI137">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/branches/develop/StructureDefinition-mii-pr-person-patient-pseudonymisiert.xlsx
+++ b/branches/develop/StructureDefinition-mii-pr-person-patient-pseudonymisiert.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-dev</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>

--- a/branches/develop/StructureDefinition-mii-pr-person-patient-pseudonymisiert.xlsx
+++ b/branches/develop/StructureDefinition-mii-pr-person-patient-pseudonymisiert.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
